--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251109_201334.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
